--- a/Projects_Track.xlsx
+++ b/Projects_Track.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Initiate_now_repos\Initiate-Now\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457C371E-33DF-40B9-B300-0F5B6E434A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623A7106-03D8-4418-A87C-E29B0D9B44DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Python_Projects" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="8">
   <si>
     <t>S.No</t>
   </si>
@@ -45,16 +45,22 @@
     <t>End Date</t>
   </si>
   <si>
-    <t>Jul 1 2026</t>
-  </si>
-  <si>
-    <t>Jul 2 2026</t>
+    <t>Serial Terminal App</t>
+  </si>
+  <si>
+    <t>In-Progress</t>
+  </si>
+  <si>
+    <t>Have Completed the base script and tested with arduino</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -98,9 +104,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -381,14 +393,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="17.5546875" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19" style="3" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" customWidth="1"/>
+    <col min="11" max="12" width="14.21875" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" customWidth="1"/>
+    <col min="14" max="14" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -398,17 +420,56 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="5">
+        <v>46218</v>
+      </c>
+      <c r="G1" s="5">
+        <v>46219</v>
+      </c>
+      <c r="H1" s="5">
+        <v>46220</v>
+      </c>
+      <c r="I1" s="5">
+        <v>46221</v>
+      </c>
+      <c r="J1" s="5">
+        <v>46222</v>
+      </c>
+      <c r="K1" s="5">
+        <v>46223</v>
+      </c>
+      <c r="L1" s="5">
+        <v>46224</v>
+      </c>
+      <c r="M1" s="5">
+        <v>46225</v>
+      </c>
+      <c r="N1" s="5">
+        <v>46226</v>
+      </c>
+      <c r="O1" s="5"/>
+    </row>
+    <row r="2" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="C2" t="s">
         <v>6</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46218</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
